--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134319154</v>
+        <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>56539</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,20 +708,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Åvaviken, Srm</t>
+          <t>NO Vinåker, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692407</v>
+        <v>692379</v>
       </c>
       <c r="R2" t="n">
-        <v>6562339</v>
+        <v>6562354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ung fruktkropp på stambasen av levande tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,6 +782,111 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134319154</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>692407</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562339</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499164</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134319154</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>92427</v>
+        <v>92454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134319154</v>
+        <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>56539</v>
+        <v>92459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,20 +713,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Åvaviken, Srm</t>
+          <t>NO Vinåker, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692407</v>
+        <v>692379</v>
       </c>
       <c r="R2" t="n">
-        <v>6562339</v>
+        <v>6562354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ung fruktkropp på stambasen av levande tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,6 +788,232 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135499164</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135829601</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57781</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>692406</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562560</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135829601</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134319154</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Åvaviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>692407</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562339</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134319154</t>
         </is>
@@ -791,6 +1022,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>92461</v>
+        <v>92475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135829601</v>
       </c>
       <c r="B3" t="n">
-        <v>57781</v>
+        <v>57783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135499164</v>
       </c>
       <c r="B2" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135829601</v>
       </c>
       <c r="B3" t="n">
-        <v>57783</v>
+        <v>57784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135829601</v>
       </c>
       <c r="B3" t="n">
-        <v>57784</v>
+        <v>57788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28861-2026 artfynd.xlsx
+++ b/artfynd/A 28861-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135829601</v>
       </c>
       <c r="B3" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
